--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104017734</v>
+        <v>110139333</v>
       </c>
       <c r="B2" t="n">
-        <v>90657</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4365</v>
+        <v>65</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+          <t>Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>661651.9491823195</v>
+        <v>661718</v>
       </c>
       <c r="R2" t="n">
-        <v>7189220.304336574</v>
+        <v>7189158</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,29 +743,39 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -780,61 +785,52 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104017733</v>
+        <v>104052117</v>
       </c>
       <c r="B3" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5448</v>
+        <v>214</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörkhövdad spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Allocalicium adaequatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Nyl.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+          <t>Sandtallskog Lycksabäcken, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>661651.9950066626</v>
+        <v>661544</v>
       </c>
       <c r="R3" t="n">
-        <v>7189219.452411931</v>
+        <v>7189157</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,19 +860,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,31 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carl Jansson</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carl Jansson, Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
-        </is>
-      </c>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104052137</v>
+        <v>104052116</v>
       </c>
       <c r="B4" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>661544.0314894104</v>
+        <v>661543</v>
       </c>
       <c r="R4" t="n">
-        <v>7189167.082604552</v>
+        <v>7189166</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +957,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,37 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104052117</v>
+        <v>104052098</v>
       </c>
       <c r="B5" t="n">
-        <v>76868</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>214</v>
+        <v>2059</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörkhövdad spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Allocalicium adaequatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) M.Prieto &amp; Wedin</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>661544.1545208655</v>
+        <v>661556</v>
       </c>
       <c r="R5" t="n">
-        <v>7189156.836391755</v>
+        <v>7189218</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1054,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104052098</v>
+        <v>104052114</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,21 +1094,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1171,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>661556.2566037292</v>
+        <v>661671</v>
       </c>
       <c r="R6" t="n">
-        <v>7189218.148992717</v>
+        <v>7189305</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,19 +1151,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,57 +1173,52 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Isak Vahlström, Carl Jansson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104052127</v>
+        <v>104017723</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>661552.3581389297</v>
+        <v>661680</v>
       </c>
       <c r="R7" t="n">
-        <v>7189211.104323096</v>
+        <v>7189134</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,19 +1248,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,27 +1265,26 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104052116</v>
+        <v>104017732</v>
       </c>
       <c r="B8" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,34 +1292,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>310</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>661542.8207076485</v>
+        <v>661618</v>
       </c>
       <c r="R8" t="n">
-        <v>7189165.735921367</v>
+        <v>7189176</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1428,19 +1349,9 @@
           <t>2022-10-07</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,15 +1366,912 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104052127</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>661552</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7189211</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Isak Vahlström</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>104017722</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>661700</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7189139</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>104017724</v>
+      </c>
+      <c r="B11" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>661681</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7189133</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>104017734</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>661652</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7189220</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>104017733</v>
+      </c>
+      <c r="B13" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>661652</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7189219</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>104052089</v>
+      </c>
+      <c r="B14" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>661668</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7189303</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>104017720</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90710</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Grubbtjärnbäcken, Mettjaur, Lycksele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>661701</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7189140</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Carl Jansson, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>104052137</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78730</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>661544</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7189167</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>104052088</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sandtallskog Lycksabäcken, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>661668</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7189303</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-10-07</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24811-2024 artfynd.xlsx
+++ b/artfynd/A 24811-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110139333</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052116</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052098</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017723</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017732</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052127</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017722</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017724</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1779,6 +1834,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017734</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1880,6 +1940,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017733</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1977,6 +2042,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052089</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2078,6 +2148,11 @@
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104017720</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2175,6 +2250,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052137</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2272,8 +2352,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104052088</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>